--- a/data/trans_orig/IP1002-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85236</t>
+          <t>84555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79374</t>
+          <t>80022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85575</t>
+          <t>85562</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166591</t>
+          <t>166769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175018</t>
+          <t>174640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404859</t>
+          <t>405391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413420</t>
+          <t>413189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467985</t>
+          <t>467800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474997</t>
+          <t>475399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>876091</t>
+          <t>876592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>887281</t>
+          <t>887167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169517</t>
+          <t>169366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>154097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326502</t>
+          <t>325987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331584</t>
+          <t>331580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>666028</t>
+          <t>665636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>676066</t>
+          <t>675450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>707332</t>
+          <t>707155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>717152</t>
+          <t>717103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1376235</t>
+          <t>1376891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1390444</t>
+          <t>1390620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86153</t>
+          <t>85965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77213</t>
+          <t>76314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82881</t>
+          <t>82833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165810</t>
+          <t>165794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172995</t>
+          <t>173035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>27244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437284</t>
+          <t>437382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446137</t>
+          <t>446289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473044</t>
+          <t>473992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485125</t>
+          <t>484857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913735</t>
+          <t>914859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928730</t>
+          <t>929057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161052</t>
+          <t>161095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164238</t>
+          <t>164211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170755</t>
+          <t>170777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327647</t>
+          <t>327762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335164</t>
+          <t>335159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25975</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38247</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689904</t>
+          <t>689410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700970</t>
+          <t>700506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>721526</t>
+          <t>721987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>735180</t>
+          <t>735429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1416182</t>
+          <t>1416046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1433535</t>
+          <t>1433601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56435</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65777</t>
+          <t>64703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>123732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461774</t>
+          <t>461743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469802</t>
+          <t>469843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476399</t>
+          <t>476732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485278</t>
+          <t>485326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>941009</t>
+          <t>941997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>953055</t>
+          <t>953633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167670</t>
+          <t>168213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172203</t>
+          <t>172201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181179</t>
+          <t>181125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186842</t>
+          <t>186852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351371</t>
+          <t>351341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358409</t>
+          <t>358428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,47 +5018,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>11636</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>25341</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>17791</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>25866</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>691713</t>
+          <t>690782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700379</t>
+          <t>700220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>728432</t>
+          <t>728537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>738887</t>
+          <t>738753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,47 +5131,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1431424</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1423874</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1437579</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,2%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1431424</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1423349</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1437084</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52255</t>
+          <t>52405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>56385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>112107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448166</t>
+          <t>447771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457030</t>
+          <t>457112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500860</t>
+          <t>502050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512465</t>
+          <t>512878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953877</t>
+          <t>953076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>967740</t>
+          <t>967828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143283</t>
+          <t>143530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148961</t>
+          <t>148972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175110</t>
+          <t>175823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182516</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322466</t>
+          <t>321943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330827</t>
+          <t>330859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>29188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>649251</t>
+          <t>648928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>659324</t>
+          <t>658962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742313</t>
+          <t>741603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755132</t>
+          <t>755294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1396412</t>
+          <t>1395704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1413033</t>
+          <t>1412657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1002-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7469</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2492</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6312</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5642</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6823</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5869</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10406</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>5869</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10943</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -836,107 +836,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83467</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79376</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85556</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88375</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84555</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90239</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>85225</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90232</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83467</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80022</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85562</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>171843</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>167306</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>175082</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>98,52%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>171843</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>166769</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>174640</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8896</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5761</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2898</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10696</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10346</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4331</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1592</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9191</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>472660</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>468095</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>475585</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>410326</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>405391</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>413189</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>405741</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>413431</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>472660</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>467800</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>475399</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>876592</t>
+          <t>876442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>887167</t>
+          <t>887101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4065</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4700</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157325</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154073</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172735</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169366</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169036</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157325</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154097</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>487</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325987</t>
+          <t>326233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331580</t>
+          <t>331581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14230</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15385</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14993</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4871</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14819</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>713453</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>707744</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>717197</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>671437</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>665636</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>675450</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>666028</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>675822</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>713453</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>707155</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>717103</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1376891</t>
+          <t>1376702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1390620</t>
+          <t>1390828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2331,67 +2331,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2427</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5924</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7223</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80920</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77233</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82875</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89462</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85965</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91264</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>91273</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80920</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76314</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82833</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165794</t>
+          <t>165645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173035</t>
+          <t>173070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12199</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6909</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18542</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7112</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3411</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12318</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3465</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13259</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12199</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7547</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18412</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>480205</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>473862</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>485495</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>442588</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>437382</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>446289</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>436441</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>446235</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>480205</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>473992</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>484857</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914859</t>
+          <t>914406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929057</t>
+          <t>928930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3071</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7116</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1238</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4245</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4048</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3071</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7350</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>168490</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>164445</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170620</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164102</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>161095</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>161292</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>168490</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>164211</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>170777</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>471</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327762</t>
+          <t>327098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335159</t>
+          <t>334910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11868</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25630</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17518</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17680</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12072</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25514</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>37320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>729614</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>721871</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>735633</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>696151</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>689410</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700506</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>689248</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>700507</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>729614</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>721987</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>735429</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2042</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1416046</t>
+          <t>1417109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1433601</t>
+          <t>1433348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,87 +3934,87 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3994</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3911</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67927</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64620</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56223</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56716</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67927</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64703</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123732</t>
+          <t>123731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12272</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5486</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2447</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10547</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12003</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>481953</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>476463</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>485275</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>706</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>466804</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>461743</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>469843</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>461140</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>469883</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>481953</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>476732</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>485326</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>941997</t>
+          <t>942458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>953633</t>
+          <t>953964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6955</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1664</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4490</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>184887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>180540</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186840</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>171039</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>168213</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>167702</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>172201</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>184887</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>181125</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186852</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>522</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351341</t>
+          <t>351690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358428</t>
+          <t>358406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4151</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13589</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12962</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16307</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>734767</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>728260</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>738804</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>696657</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>690782</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700220</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>691409</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>734767</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>728537</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>738753</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1423874</t>
+          <t>1423492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1437579</t>
+          <t>1436962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>340</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55835</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51420</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54287</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52405</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46418</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44666</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61141</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56385</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115428</t>
+          <t>102253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112107</t>
+          <t>98420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,67 +5915,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>12219</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>6583</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>20205</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>12861</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>7483</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>22235</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>468518</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>460391</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>471830</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>453775</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>447771</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>457112</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>508675</t>
+          <t>425590</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502050</t>
+          <t>420168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512878</t>
+          <t>428732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>894109</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>886123</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>899745</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>98,65%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>962450</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>953076</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>967828</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>474726</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>474726</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>474726</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515616</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515616</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515616</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>975311</t>
+          <t>906328</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>975311</t>
+          <t>906328</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>975311</t>
+          <t>906328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2387</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6021</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160930</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167558</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>147164</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143530</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148972</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180497</t>
+          <t>147700</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175823</t>
+          <t>144216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>327661</t>
+          <t>313348</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321943</t>
+          <t>308453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330859</t>
+          <t>316489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4961</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14995</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>27370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>690001</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>682674</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>694836</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>655225</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>648928</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>658962</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>750313</t>
+          <t>619708</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741603</t>
+          <t>613397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755294</t>
+          <t>623717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1405538</t>
+          <t>1309709</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395704</t>
+          <t>1300843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1412657</t>
+          <t>1316286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424892</t>
+          <t>1328213</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424892</t>
+          <t>1328213</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424892</t>
+          <t>1328213</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
